--- a/Sergio i Dome/Informe pràctica B.xlsx
+++ b/Sergio i Dome/Informe pràctica B.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uab-my.sharepoint.com/personal/1479474_uab_cat/Documents/TEACHING/UAB/2024-2025/S2_LACE/3__informes/plantilles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergio/Desktop/University/5nto/LACE/LACE/Sergio i Dome/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="288" documentId="13_ncr:1_{7938FC50-9CB9-4944-82C2-C13B3C21FA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{207C03C6-411C-4C3A-B485-D8468886641D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB62DCA-9A76-BB40-960F-59DDBFD75B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1122783-245A-4FED-BDEB-F09B1698DCDF}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="34200" windowHeight="21400" xr2:uid="{C1122783-245A-4FED-BDEB-F09B1698DCDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Pràctica A" sheetId="1" r:id="rId1"/>
     <sheet name="Càlculs" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
   <si>
     <t>Data:</t>
   </si>
@@ -253,12 +278,147 @@
       <t xml:space="preserve"> en mostre d'aigüa</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">GRUP 2.1 (G3) tarda - 2on torn </t>
+  </si>
+  <si>
+    <t>Sergio Castañeiras Morales i Domènec Huerta Estradé</t>
+  </si>
+  <si>
+    <t>T_18</t>
+  </si>
+  <si>
+    <t>mL</t>
+  </si>
+  <si>
+    <t>Mesurat amb matràs aforat (250,0 ± 0,3)</t>
+  </si>
+  <si>
+    <t>S'ha preparat una dissolució el doble de concentrada de manera que a l'hora de preparar els patrons</t>
+  </si>
+  <si>
+    <t>només s'havia d'omplir la meitat amb la solució de LiCl.</t>
+  </si>
+  <si>
+    <r>
+      <t>[K</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>] (ppm)</t>
+    </r>
+  </si>
+  <si>
+    <t>y_{avg}</t>
+  </si>
+  <si>
+    <t>S_{xx}</t>
+  </si>
+  <si>
+    <t>R^2</t>
+  </si>
+  <si>
+    <t>S_{y/x}</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">S_0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>amb LiCl</t>
+    </r>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>dof</t>
+  </si>
+  <si>
+    <r>
+      <t>S_0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> sense LiCl</t>
+    </r>
+  </si>
+  <si>
+    <t>Ssreg</t>
+  </si>
+  <si>
+    <t>Ssresid</t>
+  </si>
+  <si>
+    <t>t_{tab}</t>
+  </si>
+  <si>
+    <t>Emissions = m * [K+] + n</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>u_m</t>
+  </si>
+  <si>
+    <t>u_ n</t>
+  </si>
+  <si>
+    <t>( ± )</t>
+  </si>
+  <si>
+    <r>
+      <t>( ± ) ppm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,6 +479,23 @@
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -475,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -522,15 +699,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -550,7 +718,89 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -568,6 +818,1384 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Calibratge amb patró extern</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.7020126558685402E-2"/>
+          <c:y val="0.14161893852615504"/>
+          <c:w val="0.86670715200180881"/>
+          <c:h val="0.68883807908891115"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Calibratge amb patró extern</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Pràctica A'!$D$37:$D$41</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Pràctica A'!$E$37:$E$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-CAFB-F74C-92CF-596895EC7662}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="197386047"/>
+        <c:axId val="197385567"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="197386047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="30000">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="1" baseline="30000"/>
+                  <a:t>[K+] (ppm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="30000">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="197385567"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="197385567"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" b="1"/>
+                  <a:t>Senyal</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" b="1" baseline="0"/>
+                  <a:t> AES</a:t>
+                </a:r>
+              </a:p>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US" b="1" baseline="0"/>
+              </a:p>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="197386047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>16933</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>194733</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>232833</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>728134</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48B539A4-556E-1830-14D2-78498208B160}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16933" y="1049866"/>
+          <a:ext cx="3272367" cy="1117601"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>La mostra es tracta d'aigua de la font ubicada</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> en la primera planta de la torre C7 parell de la facultat de ciències de la Universitat Autònoma de Barcelona el dia 13 maig de 2026 a les 15:40 h</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>67733</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1016000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A1ABE25-7BDD-DBD7-0852-DE8ED7FFE7B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="67733" y="2497667"/>
+          <a:ext cx="6155267" cy="1752600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Per a la detecció de la concentració de</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0" baseline="0"/>
+            <a:t> l'ió postassi</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t> en una mostra d’aigua</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0" baseline="0"/>
+            <a:t> potable</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>, fem servir el model 55 AA de la marca Agilent, que permet quantificar la mostra mitjançant espectroscòpia d’emissió atòmica atòmica.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:br>
+            <a:rPr lang="en-GB" b="0"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Donat</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0" baseline="0"/>
+            <a:t> que fem servir l'aparell en mode d'emissió no es fa ús de cap làmpada, si més no és clau ajustar el detector en el rang del potassi amb el patró més concentrat.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-GB" b="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Després de realitzar un calibratge amb solucions patró de concentració coneguda de potassi, i mitjançant la llei de Lambert-Beer, podem quantificar la concentració de coure a partir d’una recta de regressió.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:br>
+            <a:rPr lang="en-GB" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-GB" b="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Nota: És essencial mantenir l’equip net i lliure de residus, ja que, en tractar-se d’una tècnica de quantificació atòmica, la presència d’interferències pot provocar desviacions significatives en els resultats.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>53341</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>716281</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC4E4686-D601-2A48-B656-46C5B349EDE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>8467</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>16933</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>855134</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>279400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47BAECD8-B0FD-29D5-C824-32C6BF77A2FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1981200" y="18415000"/>
+          <a:ext cx="5139267" cy="855133"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>Comento comentant</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Pràctica A"/>
+      <sheetName val="Càlculs"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="37">
+          <cell r="D37">
+            <v>0.50256871244635193</v>
+          </cell>
+          <cell r="E37">
+            <v>0.20019999999999999</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="D38">
+            <v>1.5077061373390557</v>
+          </cell>
+          <cell r="E38">
+            <v>0.43209999999999998</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="D39">
+            <v>2.0102748497854077</v>
+          </cell>
+          <cell r="E39">
+            <v>0.53569999999999995</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="D40">
+            <v>3.0154122746781113</v>
+          </cell>
+          <cell r="E40">
+            <v>0.67479999999999996</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="D41">
+            <v>4.0205496995708154</v>
+          </cell>
+          <cell r="E41">
+            <v>0.82779999999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -867,147 +2495,182 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953B08C8-5267-41A1-8A30-44F36ECBD8D8}">
-  <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M70"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="25.83203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="11.44140625" style="2"/>
+    <col min="4" max="4" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F1" s="24">
+        <v>45790</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="23" t="s">
+        <v>37</v>
+      </c>
       <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:5" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="58" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
     </row>
-    <row r="9" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="134" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="1"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="25"/>
+    </row>
+    <row r="21" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="1"/>
+      <c r="B21" s="26" t="e">
+        <f>B19*(39.098/74.56)*10^3/(B20*10^(-3))</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="27"/>
+    </row>
+    <row r="27" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="25"/>
+      <c r="C27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="1"/>
+      <c r="B28" s="25" t="e">
+        <f>B26*(6.939/42.39)*10^3/(B27*10^(-3))</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-    </row>
-    <row r="30" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="1"/>
+      <c r="B31" s="28" t="e">
+        <f>B28/2</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E31" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="1"/>
-    </row>
-    <row r="34" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="29">
+        <f>25/2</f>
+        <v>12.5</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -1018,115 +2681,249 @@
         <v>7</v>
       </c>
       <c r="D36" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-    </row>
-    <row r="38" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-    </row>
-    <row r="39" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-    </row>
-    <row r="42" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-    </row>
-    <row r="45" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+    </row>
+    <row r="37" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="30" t="e">
+        <f>$B$21/10/10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25" t="e">
+        <f>A37*B37/C37</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="J37" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="K37" s="35" t="e" cm="1">
+        <f t="array" ref="K37">LINEST(E37:E41,D37:D41,1,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L37" s="35"/>
+      <c r="M37" s="36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="30" t="e">
+        <f>$B$21/10/10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25" t="e">
+        <f>A38*B38/C38</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="J38" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="K38" s="35"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="30" t="e">
+        <f>$B$21/10/10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25" t="e">
+        <f>A39*B39/C39</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="J39" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="K39" s="37"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="30" t="e">
+        <f>$B$21/10/10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25" t="e">
+        <f>A40*B40/C40</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E40" s="7"/>
+      <c r="J40" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K40" s="36"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="30" t="e">
+        <f>$B$21/10/10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25" t="e">
+        <f>A41*B41/C41</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E41" s="7"/>
+      <c r="J41" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="K41" s="36"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="48"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+    </row>
+    <row r="45" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="10"/>
+      <c r="C45" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D45" s="32"/>
       <c r="E45" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F45" s="1"/>
-    </row>
-    <row r="46" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F45" s="30">
+        <f>L39</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="L45" s="50" t="e">
+        <f>AVERAGE(E37:E41)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="11"/>
       <c r="B46" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="10"/>
+      <c r="C46" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46" s="32"/>
       <c r="E46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F46" s="1"/>
-    </row>
-    <row r="47" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F46" s="26">
+        <f>COUNT(D37:D41)</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="L46" s="51" t="e">
+        <f>VARPA(D37:D41)*F46</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12"/>
       <c r="F47" s="13"/>
-    </row>
-    <row r="48" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K47" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="29" t="e">
+        <f>L39/K37*SQRT(1+1/F46+(C64-L45)^2/(K37^2*L46))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12"/>
       <c r="F48" s="13"/>
-    </row>
-    <row r="49" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K48" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="L48" s="29" t="e">
+        <f>L39/K37*SQRT(1+1/F46+(C67-L45)^2/(K37^2*L46))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12"/>
       <c r="F49" s="13"/>
-    </row>
-    <row r="50" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K49" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="L49" s="50" t="e">
+        <f>_xlfn.T.INV.2T(0.05,L40)</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12"/>
       <c r="F50" s="13"/>
     </row>
-    <row r="51" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12"/>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12"/>
       <c r="F52" s="13"/>
     </row>
-    <row r="53" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12"/>
       <c r="F53" s="13"/>
     </row>
-    <row r="54" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12"/>
       <c r="F54" s="13"/>
     </row>
-    <row r="55" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12"/>
       <c r="F55" s="13"/>
     </row>
-    <row r="56" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12"/>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12"/>
       <c r="F57" s="13"/>
     </row>
-    <row r="58" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="11"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -1134,25 +2931,33 @@
       <c r="E58" s="14"/>
       <c r="F58" s="15"/>
     </row>
-    <row r="60" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="16" t="s">
+    <row r="59" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="18"/>
-    </row>
-    <row r="61" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="15"/>
-    </row>
-    <row r="63" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="38"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="42"/>
+    </row>
+    <row r="60" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="40"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="44"/>
+    </row>
+    <row r="61" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="41"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="46"/>
+    </row>
+    <row r="63" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="1" t="s">
         <v>8</v>
       </c>
@@ -1166,7 +2971,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>11</v>
       </c>
@@ -1175,54 +2980,60 @@
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
     </row>
-    <row r="66" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="22" t="s">
+    <row r="66" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B66" s="19"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="21"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="18"/>
       <c r="E66" s="10"/>
     </row>
-    <row r="68" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="23" t="s">
+    <row r="68" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B68" s="24"/>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-    </row>
-    <row r="69" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="25"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-    </row>
-    <row r="70" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="24"/>
-      <c r="B70" s="24"/>
-      <c r="C70" s="24"/>
-      <c r="D70" s="24"/>
-      <c r="E70" s="24"/>
-      <c r="F70" s="24"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+    </row>
+    <row r="69" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="22"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+    </row>
+    <row r="70" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="21"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
     <mergeCell ref="A69:F69"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="B59:F61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF805755-B3F4-A041-8801-ACD56112111B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
